--- a/GFGsheet.xlsx
+++ b/GFGsheet.xlsx
@@ -12,24 +12,149 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>[B@48451216</t>
-  </si>
-  <si>
-    <t>[B@3480d44e</t>
-  </si>
-  <si>
-    <t>[B@257cee97</t>
-  </si>
-  <si>
-    <t>[B@6583bfde</t>
-  </si>
-  <si>
-    <t>[B@9d31f4e</t>
-  </si>
-  <si>
-    <t>[B@81fe861</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+  <si>
+    <t>0�?v???0+?	*�H��+??????�?`0�?\????��?����Ӡt
+?���b.��!X�?1fK����A?�=�����?��?3	��?�]T5ՠ��?��Z?���� u�D�?}!��fma�E?wj+?�;e����?ȑ-�1/��y�yR�xpÛ#��o�??���C��N�d�?c??????��?c~�??%p��A�?�?�?�]?&lt;x@R��?�g?���&amp;Zg9�!d�?(��%\d"�����?oY��u����?2�8��?�C��~?A�4Q��&amp;k�m]?�q��;_�vȃ(������r�??�4+��?0��ϣ�9 ?a?A?ٵ?D*�c��?.Gk}�j�?n^�?iU!?��?H��?��?�U��Lh�b�?}?J����?�4Y?�I?+?A?��+B�zjĭ?7��CTE�?SL��?�R����?�?�?Iv�mB?$۾?&gt;*��?�~�nMi��{J?�?@o�??�x�p	����gOt?o�?���9n�ܸ-U,fW��??������?;?�۱ffĎ���?L�cL�k�?@v��Bg΄?�Pd�
+�:6�&gt;���r?��!@?Dʕо�????@N���X��O��?�ȗ��&amp;�?��J�9?A?��$=��24��0?���ʟxB=ݳ(g�;�����ї�|P�K�?�:.�N�0�
+�ԁ�\�L�bg��H�</t>
+  </si>
+  <si>
+    <t>0�?v???0+?	*�H��+??????�?`0�?\????��?�?s�Cu�.�"�?X�P���&amp;�	�z�*?\s�r�uAU&gt;OF?K�|�9?�,�?��r�)???�t�!���ZY6����[�(�?�����Q�7��W?1q�@Q�	����?��Z�??N�].�[�}c��ψ3�)��??????��O�5|����@`u�)A6�?;?���%%�Y�o{?̠Vt�]c	?�?A�DWP����q?�.}��F'�?R??�e�t���a?I�?݀&amp;l� �g	��~����n�Q?+2�:/[�&gt;��?�q��w"�^�?�f�#?_��&gt;%?A?��C.c���k��|\Փj�&gt;?��E��}��osǨ_A�?S?�?���2�q|?�0����;G����,Ϣ�?A?�ܙ���LD)y�N�i%+s5&amp;����U�����:MӃ�Xv�?@�g��P�N?�$�DhlRV�W��(���?@^�?����?U���?���D�7Z�o|�?O�u}~�A "J�Nb2J?��M�%o�?��Ҹ.e�ô��L��?@N?��*^�"�w?��R?��au0�&amp;^GB�~��.�?���jrH^�?t�?��ǃ?t�}��u\?��O�?A?��
+[�^�&amp;y:�dF+�Y�?�B��?֏�	��tUl�m���&lt;845�?5�k?� \�l.�Ir&amp;dF�5D�</t>
+  </si>
+  <si>
+    <t>0�?w???0+?	*�H��+??????�?a0�?]????��?�8�?�'?�?�ĕb?e"�RxA�F���6��&amp;���I?�/�?Uo8�?�w!���Bt?$�BUu!�??�$�"�"L?�!�A�O7?U?M����z�?&gt;X����t�3:�ݏ$?�?�u�?F�tA�e"���#2?tJR���??????��?g6
+~x&lt;����پ�Z����z3�SK�?�?��N�p��R�?�&gt;�9�Ha����+J�L�cN��x���9g*���ܐz�h?_??ǈ�5SV?�+^��l???ޡ?�9?~�¯5?�?e!�???sFj�z���W-=?A?�nj�?��&lt;9S]$a?GhP����%=�E獞g��W�P�??��?�G9??{y��qPk#O?�?}���h�?A?�K�??��=?���Pr�5�:&lt;�???�����軟��X�Sd�G,;���^�&lt;?�??�QI���f�7���o?A?�\��?_?�?�?k䦩x��.��??;��s�]s�w}L�U?�_8�4J1�b??�?✩�U}�|���K�?@d����k��� 0��7��?\?�?��?�%??$K�@�Y�?b�?{5�*C��E"�?�a���?H+����?A?�|��)�H���?,��M	��|�N���?样"�O�JG뿏|�Y3�����:?��^d4_6�-��?J�</t>
+  </si>
+  <si>
+    <t>MIICeAIBADANBgkqhkiG9w0BAQEFAASCAmIwggJeAgEAAoGBAKZpBcuNTQZF5F4cTpKIyjuKHAdh3HY+lWTymd2vUuXE3roFv6nOLxEPxvrHJr7Ll5oYbGsqslvAhyC9kG6aQnNCjswZwFos5/E7RNyy919AFbPnffrZbwGfD+VIy9csVHdzSv88mKpUWr0GZJ9qi6QSXuqBplwFrLub3O7PQVgJAgMBAAECgYAYiT2ogKINvbppQeU35+FhnAB7+irmaF3gr4COVi5z4G4yoWxcHiGEc34UNc75rM0ilF1QA9CehKmn4ytrk2UempoXwwqqXPyBkrPL1LcJprmub8k8sMU0nX0rT5VxNX71waTdKOZ66pCpf0jpz1RAMsv3GW8Djrxj5qCRkpPAbQJBANSuVpWdO1zmZ9cdz07IoeFn9aWwAtcLrRJHLwpHkYYLm8kMrdVnxJQzaVLmA7pZO/RduwILJ98iKWVqBG2TjC8CQQDITgYOrumEqfaQA82A7kXkv/4Q2sCPR447naPPz04g/qvosnDvjxxZ4EWHZk/Oczh7XGcs/6on+SloHEdeETlHAkEAg1LfDeUXaaavicnTXy9NndRGfzdumYCRLo8bwbotZlq2p+8XS4WWgXg5WcHDnYZKGfriZUGkLgh3DTLoZwzLawJBAIiOILUL6+lkkdJWtVhLmNy9QzEsYRCNINtluhLnaoU1+e7XEAVRlGt1aRFI3+mIRZ5cPX7BAbjktaTjeogXx+sCQQCxKVoCM+WyIboG8RyWqBMl/m+8k03jCs8SFfrWPZKKFSeoMyjj1arBMcyZaXUi6U9HkhtYfIDJYv4lnitVVqbk</t>
+  </si>
+  <si>
+    <t>MIICdwIBADANBgkqhkiG9w0BAQEFAASCAmEwggJdAgEAAoGBAIQWT8wmaSGqlj2lL7PMFiXI/g71evxiaTU3tUkE9XqP0mjJU1G0UQN1wsF/Vop0PgaM/kDaUmwfElW1JMyg+lFd22yE9jO6rAnP5EZeHjfv99pWlRB0KOq1bYYvITPqz/cI0KWhzpgaMBZp9qORDF5SqNC4sv/lGteVl7FRGklPAgMBAAECgYAiHqVURePIV4lhuSbeWeyqrAW8lXrEcSNeJNrGVuqWU0p12POV2m9G5od9dkhDkY1oIcmXtQ2vckNJMnakCT0/ojdCyCIlAQvKkfw1mC0wpT8HmTfDOVVq84Datj2ZrSQD8cFVB3n2ffzl9Uxef8k1WXFQD2t/D0JB5V/7sibseQJBAMTVraepyqDic9WWtNeAYlHNO0U+1D6CaG+ETDGO06nbRQ+dhZVDQGYSfgSRYTucfhdl/3qWiF3imfrRWVjHQA0CQQCrylixw27+0/r+9sJwiq12Xs9F2Zu38mL8peKVg0FZK7kJ81/Kgbm5mVbavLZsPtFyjVSzuLcPMRXqOjzHVbvLAkEAmep4+2VzFHFfoMJTMTysJUk1ssUZlLPG1IUAS7Ri4SycCUTlAz3uaqLFNe80uDd8BfH1X7e8dKXQQGhZ1GkiNQJAXitUhVVhQdVH0H3JxlFuluWP73VC9Amtk1sHovfJWa0rCLZdey+zdHcG8m7h/OJOg+HPXZlS18QLhFMaQBbSEwJBAJsb7juTBeDZ7tsbyUXJPc9NrPXdxqLiibNPfXdU6YNm+grZ01LY9VxeBp/CTw+l8N3Z61jVUE+C/b4OaauvM1s=</t>
+  </si>
+  <si>
+    <t>MIICdwIBADANBgkqhkiG9w0BAQEFAASCAmEwggJdAgEAAoGBAI7lth3u2MqX08NZ98Rj0bodDWcvPdT3eFwxWTU8WO9wza2v1YNKBMuupNuI/QCc1+df88Iw5f62d6CD7FoyVoIREDC/wZN7JmIJ+acNKhQWrR6tMKnQgTIrvoH71Krh/h+bpm1IJh7Xtcs9vAZNQeuPV8Xuyt8NUIpOAFgJ0eb3AgMBAAECgYA/YC3XNLk9kPzAZUR3+3Vmv7/UBaW8sEzXRqOz8qHXAAaYg6WEZu2dkEVZgHYFMYqn+WxYsesvfqmrrRbEIhMvS5zOVXr9g31tqx3gmNL3n4agoi8nPtmWPkFffjXc3fLvWmrYQ0Uq6T4d24rMF00Qt13ZEQ6kU/B5C0KnMHM08QJBAJ2UaUunmi50PGI04phfX1DaZtIaVEIzebbE22RrNbebjMig14kmES6UJ3DINQyLdm8aHTlID4SMKVPWEaeIxnMCQQDoJbZYxNBSmzO5mV3KEf2NzhD/o/Jmif1eV9vB57sQWglPHkr8lmoDT8OZTJnDsDQ6aXJAub1ruvs3m/Vu0vhtAkBvErShyjLoua/yfVqXkupJwJinUj3AKC6MAPiwMM29bRxwMseaecW0smOWoNibzhYePCcLQFsH0BA1cvggwk03AkEAq84tM2kFG/2MvFEKnl/OHMJixi8ZWFXLU6UGGG1dfe6EcS9kI6dV8fl4Mt4D9lVTcd9UFR7hVvdcsH0VmN09yQJBAJqjdh+ZNhqYuRQsrQhcao7KhDDFrSCyp25hqNgFo+Q/uhXVZ/dBBl3kg+JHSxXcfzZDR62G+bLqhddbEl391r0=</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAMxnzVZGP1vR2mP/NAapiOo2genoTSQgjH0amwMQq8xrHfi562gFv4Vbr0/eSm0pObydi+7tc8BG/hhGhzA5vcdn+o7GJolYWOZf6OTP53dv38oAyf+6sNT9dROMDzZUXm6+AioGwjyTAl+gHB/Gr/0uSrgSuYSF9GVF0UadLjYtAgMBAAECgYAzDC1kwXBrTvJajM6CZ26RB4HUV7aEMjjDuZRC5LPy/kFi75ORy/WzqV0T9jDiKCyKJVJgHh8NQu2MRHjYm2MAafvCH+NhL6husFxi0pC4vr3NLatdsYfWL54qJ5KdqESb4OMA3SR28TJEGe7SsK6AaeCn+Pza6ht1owyQ3PXBwQJBAPtqJYysHkQ7+mvkfokSbpt+Wws9RJrWP56uA2qlUm5Xk6WXDZxgrtva0nviRdSB9Yvo1eQ5XAnN6phx21Dv93ECQQDQIiuCf8w1w2LIaIQi9VQqiiIXP4Eo3tujn/KmojHvODugE54sQ711MTKDW2xfDi7LRHb3cjksu+NjJuSiXqR9AkBtobHSD9P66TSgC7lpyFHXGFhXJFZgNoDzjuoKfSDe4O2PTbkvsbFOSbNzNg5BRpJueg+bP6/0zog4BZ4fQyThAkEAo+qlVauMirMMc0VM+7M2zCHp42FSOXv6gw0PL4kBxqME4ndQ1Q+sgEV0wNsZqGslE1UiVJMS0FZRKN+SpQXgiQJAVe0QPTZprszCEHqd59OBmwLjt3WzfdLEVJjH/OIaLHM76dTh+kVvJ+nOFlT6Len7LXnGfCE+2rvB2c06NILaJg==</t>
+  </si>
+  <si>
+    <t>MIICdAIBADANBgkqhkiG9w0BAQEFAASCAl4wggJaAgEAAoGBALsIrXULSf9JBLG66YQ5i05vAq2MF6ECLRTHfXY5z0Wv/dmjN/oFaZh4geH3XXScGutTkcP6HWLk0LYQIAnlTG8v4LIUN3lQs8eFXkUOY3HU2mvYVejMzPg4kSIAolXQ1MGNIBhPv4n+bZ6Gf8hoPXmS9UZWRMACTEVigyPk39rBAgMBAAECfyo78+9Rp/LuuzPWA2DrhAMncE8ZxHfqXVkJMydFryQcTwEDD7hSYrK4LkbJhgqVYEMMGdOx8bDUQyJRFy9HAJ9rHeP+G05NrmV5uKwAW9Px04yZF8Vnp9P6yJbWKsr16GESxmCVNHf7iqmk1kLQbaoXPmOmFhXqQp6a5Byk7IkCQQDOO7eBM00PIpMfdwQBzdBdh2MrPkkDGIlyBwzKzwH3pAsyWfC/9D6aSpGbDlfH5TLbK4mXYOpmiiZmDioY1/oZAkEA6CrmFpbx8M40/uaQjJ1423+kAYaegZZ3/j/SxLmMoYAZrA3t4lC7J0YqsOps0f2DtVpzYLWzSDogLFkAblJK6QJBALEmfLefwJa6pVQG4MtH5q8gh9/ybbcaEZ6ATc28Sb1WDUQgG/xXKptQaIifpmmQCMJZQKRm3JJeIyPREPosM6kCQBrSEeCcMXkDKWYlFp/X9UVOOpEejyMjUdtiXiPx14g0t0KEHW4eq3A/D+F+Q3IC2ntR5rBObVazuFHHOmCESzkCQAn3+evAJyYCWBtQUkjlOqn74q4vhx+Hqt0jlMX/DWZ43lF8hg+vx2PXJy6zZm6HyJNnf39JbR1w2zOlBcuy/p4=</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAIZUfPo5N9o4PuCubuFYkGnN8gfFKmJhEaN91X2yHe8BIGEGYI53Shgnu7kxKOHnCXG/gXrnzBZ2q3HYrjM1gnBunjQ4XJaGgO945gQ1VtQKto4N3p1127JhIRAUyokpnaVTiAtrTSE1OOEBv7YfdPiM9fmzzvB13WXGWS5xSzZHAgMBAAECgYATIzX7oiuPtoQCwjyAH1F9Dr8EwLVv9vtVKwgU6cuI8Zn5fg1DOWyAHNJfqR4gHP3D9lrN4KM7Wg8aikUQfPbxs+iVN1pphufJ2mYaR7n9fbaqKP/WlBQ68nIJY1o+SVKW9iELYtaEE539GZLv4RNPVWhKDBMR3qtGM0V9hYy1iQJBAJUNeOtaZLmSbA3rxsb3/dErfy+A5rD5H3KyUmSPTapRcAwwQoEhazUtPDJrrsdz2WHiTeDdUD9YFWNXK0Lr8QkCQQDmtrddDKA7kKKbCdTcykrR7gX2WkCmFyXWnHFTshPnR8bfeR7XoSjWiXcGMPPtPKiS2gjc0NgfF6rTITYCTNDPAkAvMvn0hUZaIUzIR75FaWhdoUmAMHBc4DaeKmu+3kY4xdsWcP3OSFfbmfxy9vh8vmm6/l+s8kgkFu+G6qaPZYmJAkEAm/ZiqD1TyFBzC9mukv8Ray67yxih4WV+h8DD/28/czabYxCO3/erErRkyMOo8fPyhSttmFB5+TLXoNgvmYhyEwJADvv4hLSw3e6sHz3glIzwg1WjoMqfygpzkxJOYEtT8VRw3/X4pvvdaVgheUsEhUI8z/nIVpQB8OXu7PByhjBQYw==</t>
+  </si>
+  <si>
+    <t>MIICdwIBADANBgkqhkiG9w0BAQEFAASCAmEwggJdAgEAAoGBAK+A2wOTxhe83ZxISnR5iY7JdMLXY4mIFZsf8H7pv7Vwj5lmHVRbZgeC3AGEYAOwEeqEMs2SsS0Ybgtk+SwFdkd+828QGTpPwzip1eIT9ErhfcQiD/18tJm+peMIZThppxxvRvhm/vS7KZK8EfiSf8lfu27qLBjdwrAYAlhbFg9RAgMBAAECgYADZpc32kbyIk7WrqrsrLHkQlXrdEeBkdFosbApZrz4K9Ud10CgaBX8dXDEbGzSMs5MvEuMuA02rxIWJpp9G8z8fNIZBLu/kXiIix3xy1kOTSiPDivB1dIxSnUvmbHDYwPk+GOrxhYg2IDKg/qJlkVhLEX4pABngLIQobw0FpzirQJBAP8uXFiprx3X87oJCKMbikbkYe+kDJuGO8mR1iFJFnMtOcEOdS4TnW7flGfjttSZoa+A8joa4PF4CnK8yOV0f4UCQQCwEQl6QBfKxPtCdCbXkbZ/g4TBsA9FISyOBWgg8ViWYSkHKOgzHBr62n6nBc7xQqUUNDAfljcdAwi7mOKrG4xdAkEA0b7dkNMIaVNTthouy0KbyeF2zm7dHgibo/cHNpzIoysNSa4Eizb8NGH5rdryMJWG3Kb0cuYc9t1gWSbrSg8TsQJBAKe20uxc+Uzx7tYShp158/nrch5+c01KmIKAq/wVaml1C/wB/44QC7NBRrwbUFGJRm7Ed8Le+IjuRvdMXz7W8xECQBZVjHhhvKgB2HdCI7yMQtRObsJVqM2HFmBSou2ECX873gwJvyPRkj+EcYSR0BZlcx3SEHMqhjKQHUzFRMcpq5w=</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBALdS+VQSDuDrq/CcP9zK0PsO7KuNMvs4SQz/pOg5oinGTubFHAtc/d9OYMMRwBk9nSgdIzYwsBGAwJ30hNXwvNEKO3IXrSWKJEih8aJaICSzjMoAlEqi3UQmQB+vXNFNDd7KA6hRsWpyvlmNxg4ZdfiFQxzfonqLoxW0+p1645d3AgMBAAECgYA8wU9nKMrsiL5FcgsKKd8jbRlLa3KrZkZze9/TpJIVJSct/MIkE/ABCzEvRNk0pEJKsoliYrVfP5vWXVyOqIdyciGJ7BX0qox6dKcAQeHeIG/8ypDz6l+Ch+PwxW5HLP4ij3lH8yIvoGgBvQIU5BgS1vFwEjAqgml7HAfaPMCeEQJBAOL/ZDnp9z6kayhARJ6j591j6BHL3eHZiX9HLWYC0nXIimPT19f6XcsifbDVuqvZ0OtkxGlfy+gbLY+f4svHLFECQQDOvx14ZhM+mOfjJ4K4YMfSMTB++NCqXg6jnpaO+YO/8oEayJmA6MAqCcqJWBjAjxQEcKou47oGFcPELIpE5z1HAkAOp5xJ3N/4bFb6r0N+1mgWs+d8lqPJe+jTjb3RkycRMZQ1o6yQpfo+LgjdTL8Tbyl8uPGxN90LLA4B8rmKnF4xAkAMa3y4u+ESFJtxkPEQZHf8j4nrRsU6RtY4TBGdWy3n/Qh2dHCMRu8sV1Q8dfdesfmw3pfKo1GMhggxo79WrlGHAkAIxLJUBk0LVENjO07f0Mj6QSB4At1giXhkWcXaVH9Q1knx8QerTJ6wBPWCpNrHpwWCEmIn3aoyusv3bHLzF2n3</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAMpFa1KmwLcgTzkGKRd0tCaLdCiiKP0Ih3k81oh7+y39V1sAcxu/xid+mi8E8olKGAgtfF//sAe3Hi2aGrYsgp9bjv+HTuLj3wu4t0AJuCTkMmEpAjoHZrW67OIxEIBsVRKuFx4QyynGO0vIJL+3iE8QSTYxr3J7ZBialoeAEEgbAgMBAAECgYANWebUV1//rU2R9wP96sqOg5/1WqkX9OsrJ6IqF9has3yoNO/R3YKRBRfckc7jZd59E7Jk+hEsU3we4+JuoMbtxuSEC8DbUXsYcKA79/ZtB7SpEEf9LvyLD0gy7HXakDHHtMywPT942ERqaHN+odk2/ZEXUfvRxhTdMzeqCTpBMQJBAPWPOR5ak8WLT6XYxZNvweL+PDPF11vktngLJMaKgFzNXIe+lRQAW17R5nA2JFiDFTQEjLY6srsTvLGtxiq2rOMCQQDS3wb9/4yAPm9VwrjXjLsBK9j75zDcDP9ZAgXHRSfRUjPhHelpKFq3R45lcGgtjB8XMn4ILxe/cpk7Og+GFFVpAkEA6t2pGSIzMn+Tl6HlH6aFwLHALRiuaiMwb1LhQtCYA6scNG2RswbAXcnPaUYvr0T5E77CQ02TQ6GWGi+GWbZNVwJAZlDu/JldW/BvZwZXV8ciCZxz6S4xJ+RqlY6ErT6h5k/jekxgL7Tz51AiCJg1BDyj7UaDnobzF+KL9Q/j7mO5WQJAah5Ka3icbtq1ihZudc+ODMojGriKzpsOQGOK2FP97TKvETyFe0ZCbV3BCNX9Dj9P8rPPCNrI+tDzDQFiD29Ypw==</t>
+  </si>
+  <si>
+    <t>MIICdwIBADANBgkqhkiG9w0BAQEFAASCAmEwggJdAgEAAoGBAMMPpM0yS31qGGqYS9qvOskdqfZbe/4kbWK2vspXRvtXOmjtl4cNydtj5l9lTBiDKjp+E3hBKv0khWD0MlzJgdydojeEEjOruwDUOZfBLd9ZjkRAmoANA3XK0kd+4YFDcNPIoEJM5BFZIk1Wb0e3PGPgK98dBFLvRqLwBl1FYYRZAgMBAAECgYANybbL/GCiqlO0gTRnblh469xeOiQ/GCMVRbahxd6SGJ3b2eOKm9pnZB3eI2JoHylmfg/xQaYAw8qbylcfAO1pY7GfF9Xi9KLOJzDm2LwndsR+VXy4oE5IhKVL4ItGOCyjT1P4IU5f4oMTYHkW+luiwC2DF1UtbknS6V38wdQXaQJBAN61HUqF/lQCK3lVtNLFrIav53VUY53yt3lvvOBv9xutApULe47FrwDHa10TK3E6PIc9qeOTkq2n3E3CZn/9k90CQQDgOITTuqPIMV70/AijzbshkEy2xMrWoYLjSUIKnCjXnZrFQ2fe434CiSSW4p7G5m8WYX8lQUtTCo2JtQzbuXitAkAxcLmo8qgsVDL8g7dZ10JewCw9Etful5R9o/2lQZX1Eepx1hO+9UnNfXfrOLc7Mrd/OoQ9nmRAovQ4WwDQRyYNAkEAohK4kIM8mBx30wXLCPxQ47X2fbZKGFKu1bPCdQDj1NcrZKOQlWBDWXngZOByfLtcWQUobrl/xQq/vGaOYNT0EQJBAMNKh5SovWvr9N8y1WJzsgdumOBB3Ecfj5p6+3omnEHwlyhma7zt+Q6ZghNEFg5tgI95267Ys9SjTXrdwsyyHqc=</t>
+  </si>
+  <si>
+    <t>MIICdAIBADANBgkqhkiG9w0BAQEFAASCAl4wggJaAgEAAoGBAJLp1KKtSqYDcf3E2qjJz9Q3ZhCzBegpLBajlGKzq5/FJ/TNX3XDnzd7R/qWgTjyirf4X41v4u1aevBJICg8XIrGVQ4WqDT+ILjzzRGpahFeGjUt/26rpkUVVWRodmzIvgTM/jtrbpnZIUzpYbKSMAiSAXJAQ/FpixGTLiqAXhXBAgMBAAECf2F7xJs9ScSRkgNwVXdH58lKs/BuGi6hmJ5dD4p+62l/YAf8eVSh6ErfBDVZxjKMyKdSU8p8wk36NTauudEjsci5VWS5EgMaosvYB02plGH46QKuPuYJHKvqba8HaWREeUje3P0b2RqenoAaOB87pC2gHj6xNNE0Ix9yflHi2wECQQCjSs9diWCEAf8qGpVGcWZ0J30NSZr8W8R3AKcyO4mhPwaNk53ct+Xvnn2a6hkT6eeA6YzAdJTkMl2autLG/I0BAkEA5lJ9/w5Se8PXbuU6gOVehLE2cM8zl+qAU1Sw9/PQrp4tga8JYlhZbcU4m0EMG6EZ6BcUTpVBc47zb+N1Ks/IwQJAFc3UeKnyYE4f81BPZHOZ+aKYOSD99/qM9lL5AGUg0I4o4ti2OJW5t1BTd08RAC64gectqzkl9H6hLxsJMBbjAQJADBGCfJzZgZavcSYdvKdIHpfSjHKu92TYOIWViEiERMIRDFyJl1edx/yvjKMJ6WC1pM2gyMVVWqLA6rn2Z7nfgQJBAJ8w4ZizLr+ZZCpUgCQR7Iw6JJVbq6MdIk0vsZpxkicus29kiBQ4IWRlM5oOZWw7D/m7zomUuKOHJf8tgJc9LIo=</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAKJBGnxffop29YuxOAB1H9BOqWSUisVqPz2U02vo8YkiVhhi/dJfbLtO/vjOnsLajShaDwbQhKA954xdhyEukDVeMnN8AhCjaRa+rcs43t/57wVKpgMCqJOm2bCdIroUfVtknWUI4AnAiykQX+vQeEO7F96IusyJuSFtKdvMx6jfAgMBAAECgYBFuo3L2mwyzFnM/U2wYKVZ65w/ldina3gfGmjbrKG0ifWPCGfFc23yd0n7Giy/V5YnO8DOcGk2xjPOrlkGyRB+t7UgRrV0aFNGr7Bo+Mn25coh4MZ5gVasAk92E0JUCZhKtjVE1TEHIXehydGEpPHxrZXSHJ5QaQE37Q2iwMN0FQJBANAFBf+4Iw/iA3tm2DsryNX5V/Oyu2GIB8iSxzyBStAu3gDRwBpl9h1wcU3a98EJ2bbPQfSxgS17KeaabXqMi3UCQQDHrcQzTrQXjgv4BSYuV6YVYBhOIode9Eu0uY2uV3+QnmIilVbEYoXjGKb1W8Kh1HAHdd3CYlWdaGIrdMJ7PZyDAkAHsnfjW3PorYtFcKvFnLwktsI7YTyvwjHPiSbYJUyYYXOTgi9iiq1Nr5Bxug161ht5OTgOjtbh0PHe943ff/3VAkA6TcK8OH7dYdyczuQXJACavTRbnDlqwGpamtOD1Iiq8ZQ2BOUQ8rOlW81kVya9mgocI45c89mL3K7NgYpH8fWBAkABJ7mIvlFoljkAp3vbqbePbaSYpLPtU+eWRdX/2SXRQUEdoW5LluQgVLeF0/BJgMphGt600tdOU0cfrz0a2MPw</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBALXQEcOWnqXU3hJxNEbFceMfsjdJ1NxhYpFi9tXa/5qfspNzAwvOELVuClo9d05E+w6TgNkUpclzrmPNLP/EueI5Muacgyb5KF1JkPOHroj4lLBwzTCk9g9MhroXd1R2hykqIs9VW9Q8eIkG4H4qEBG8NxzYa0KHAXV7pS6rUQd5AgMBAAECgYBaIB1eLkDQhZfb3oACgQe2hdTLMW8yG5hH553iXuAL3xQfoYimBm0j8rtxBj0o8GrfS+E4OtL/7LdKw7+FvhhCJONvLrdK5sonWmA1AaVSzNc4NejXQ0fEGearI+xjRV1bzG7FWykxpicbkQoYEqqKo06MPrPB6aqz1LNmWSAi/QJBAM2hjXWMyC7zUHCcus6jKNmNpX50MQyvhwOkIp02kWk5POCkQoFtGn1mOPglUCYTgYB9VZ38sTGsv1NafFraTrMCQQDiWPMy13/IeSIGYtbMXSCzeOLD4OGOFhs2GdCgh7x5W+CYPkotwM9TwTSQE9Be4uNCS9TBoV2e9R1L6Gx6GScjAkByL0uGAu8GY0Y/wkhZhnCgne9QEOVLzgyDERnHgw2sCIStmYj0pckX6TOpV87x1dMLro1kdXVPyEVV2+FB8gfRAkBYm+nZJXPoz0L6rQbZyjtbBx/+/rJOJWlRrJl3vquR9t3du8TeVHTVnPUu0hLoknnVIkqP4tP7volRhhOxWNdxAkBo6l0shyYfrMKT8BwQlc35vGi7URcHRoByQzeDocMoKOUXrHFjevopzHOaZdMyU2qZPSeAJgl41PjoEg3IqV/A</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAMlpZ5bUfItuGv+MopistqILM2vWb/WGBRI9o8UJcqAF7FmmdYa4Ljvme/+ROMdsKtW/Qk1rWZGfmbYONkOXr/12WZjIEdvPhnAOwVUdbO9AR0t31c+kLaHaIMokEZJ9hb86zzOG0JlhjV0ylIULWluVTw/CSSyHSnFIiY6zVYF3AgMBAAECgYAJefOdRZ8cglAz4N6Pl2S6aBOByeOXpjgb3RmU/jZN8CloKGxUK9tFBzmjUyZcP6seRnLsqJXcw6kcRzvnXz4w9dHbsOpMD26q+gah136f5iWAQgitdwzWZNxWOqPyWsE/rj4sLkHa2CsILkqAoRnd7b73+alZmgGoZWPwCaVLVQJBANNZ0M2fdSBla1WFlZ60jQbbMxZjndMhUV66xfi6RCrlu+76CoMwwy8s4fPzC1Fvo4tCytp780+iqNhHB9i0vjMCQQDz9hEOlLEDARqVe6+1zvmCqAuiQCHQ22CSawgdYO/eLWfWU5GA/EYb+Jdcy1NR2TLcmgMEKxmjpWzHEuC4ECOtAkBOy1BWKJmxHz553tieF2/wW25bbX4chXJhn75I8aCSYZ3EBYI/0MEj6FbA7R6OGNHfDGK2O7nFOb47C5g4SYITAkBEx9JFRxyk2THShT2jx4fHE3O8OdKO3NrcTPrLtaHLBQgqgAMc14M4rZyXF+gUwmS5l15UVYZ0AdaqRaM/oaU9AkAhQrw0bHWSMovKo8q6KvNIDUI7uIiI8DA3ufrUHUDLQJfFxpvmGJZKokiyDq2TnwmQqIGnXH3clU56DsEq1H5x</t>
+  </si>
+  <si>
+    <t>MIICeAIBADANBgkqhkiG9w0BAQEFAASCAmIwggJeAgEAAoGBAPA/K9cHZ2wLyGfUAfTJNFfyAcSiMJF/BxSn+extSJseYM5sMyfMqlTBja8uYF8SzFYJAKDgixyvzilZWwZfVgEy38e5t+DZK0GFT33KfdP6BZq21qoY9L8ZoQSeIgAft+OjWcfIZt5Zt20wB2Xg5F+BkfLS2JVe9qSkzXQQmN1RAgMBAAECgYABT9j/kDnpekF+hqb5lRkw80B8+EVDYCIT4+xulPSw6ygsbGUVni2eb52kU6ChWEcPH7a2Ci/cSN37dhJUDTR5I747WFx6sGb2+pUbxyTwroVedKXisfrUZS62LJL+bQyT2C5nHQixfOEN35I5ddzzOnjsnPg3VDhdSzDVabHzwQJBAP6ten12OUa6kA8oS/UUZr2/D2SSsbGPqRztxmFDdA/8rIvkKtUnGaThRRl4tTXkJ0znwsrjegJ+3j0UqgF9CuECQQDxfoLRnlf8jqS7B+jHN6gZdMoUadD6YMs538kqazMPo69wswKph3cKd7sWwXTJG9+PUEM9/3HIhhJesGY/2RBxAkEA1s6hqyLFaqe/DFnTv1JG2jJFnHGymO5wGGthUPZg9X8MVi3MBt8k3RH4g2Rxi5P1pgMxJIm7hlFVx7UfM4QxYQJBAMk/i5dSZLKk0OTIP5WdbSnhqPIACNZOya1uL/94nHHBD9hUZbiPmoWPp8rb5w4de128Hn1RHipkiHR+fodgxhECQQDDDUsI5igYezxCcsWkIt5kcOWFPMpyW+pZ+zMyH4aNLd5uc2Cvw736zg8sbo2QykFBG2UKmZ6WJ4h+2CTXUi6F</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAIhQoJalgPgkrjUUdSt6vT5TYDznVwQeq+YIAXe+xQFQel9naPhxB5w1ffjl9/ogurWdtCTlX03ZWZz06MhNBJlvzlTK1PBZzyqTY/N9a/B3dozGv7y3dOBZSwjeVTm/dWxd57Uszm1sycFZtJw/eG/iaIbhLWsUeuWLxNRBfIHFAgMBAAECgYAVVW8InK7eRxlXl9PNofg3pqNXbMpOzAERr3uRUtMwxThdsYi5ZzEudqW4PD+OzywBbATLSHWdsLBIcwDyhjE7mlzCUrXZLIGpJcdLVMx4CzKF7BuKDp3dTAGzaGGe3YHxGFiVMLVLizppHGnm8t8Y8CDRXyMO2MZ6AZyAieBciQJBAKU4kpg3NtI/0zs9huuix/J7n/kGj+se1CzSe7Pc6u8kMQJltH4oQe3lsaVQ0RjDUJgWspQXlog1y23LG63p3KkCQQDTNjqdMAA3sD76vek7Y2qIResI0973IW318pkBySnHAZDcQvLak95YpfeJPC44RXjc95VK9ZIpIvHRfOV8vnG9AkAatI81XU9WIozg+WvycGhDMGpGFSJ0DZKcABWQl/e9Was2SPwonBcz/bl+EBcMGp3PR3Pr7fgd4hwUjgzWSoOpAkAxJBzfFZv3WPpOPIFXX/oZWqskkqb9uLlsz9TppXQi6SpbFPiMAntpBLRjKa1XSlKklrYViq1HBOpeY0DBlU3BAkAkVWNW8LMdptImPJSvnFMfdddWVtJiZNS5S9lPVIm2xLsz4KDwbgzSPPE3/6eqyyjuh7mjz7TtrMv+wndzW2hJ</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAJ6Eu+L4wc0elVCuCJ1iva9+a4O1A7JKqFKUPoKX05mXNdGUpQ4cldN7guYQuaNufVYjZM9ie7cWHfDVxSE72i8wOKFV5/yFHPH7d6LVTwV8UyPsBO34WP4LaIgWhG19MAk4Ca5xNXRc4G+PDot2E+tSvwv6AO+PJj+Dq7HMclHBAgMBAAECgYAm7GBHPf42a+tNlYI7hRafHDtxqnW3JoJYzppfzkCQvvKh3O4/fhDjDjmo3NP8d6GykDvNeXj3zqg47gC65Zuv5iNFI9R5yC3HWraofbPxzeo6D/E9RbZgbQtj9hMjkJhhN0gXyVJValAEQSVt+1lfPQdTQ1dMguIn5QmqXB0FLQJBAM3LbRGUM4WihQzyVPuRJcuBk9/6xnkItlSgHm9usr3d1BLMeS+M7z+kF5v0qYn9Mgwq8Ng4hOBrsaVhkZszbBUCQQDFMMCUjxDJHFfqwRWLoAedYNEtQ2aaLSP5K8ifJicOHZ8u+l5KDU2YkNPPEumjJMgCItmtvjCneM4IAhAYwb39AkBvkZu97gTIrEVJsY9VG2nMHKHYyhITyB9hXbViYDdTLBIvZt9EYjnK3OFX0Zqgjr41TopoDqwrJveWW4EfDQ/JAkAC9rWeRfwxmZx0qcxCGfijU+Yw8Pdkz9LfltngEnm5y5Yt5ZNvN334Eg0s6pLaYd4jshRleRtQGQ+3rRhC1v6dAkAZdUWkbVV4ZcmgTIc0kkS+Pq3t5kyDyqh0dIB06us9+D+u0zffXMjIfPDFGqLa/XM6HfDQc90hl6C9ifjYMrdi</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAKexOnahjqVCLMqsGexAbOxvmbXN31vBz7ZaHU1B37NCZ2J5KwBUhznNS+bn6NcCzHaLo7ncnTEWWBnc2sw+5Z6DaQcfpGgCj1AKKShQLsos/2LiH6DScIKCIF4BLH7bUDh3s5zlK2Tedwem2JNmPVHcFzU30ztX+UjI+/qXB6pjAgMBAAECgYApfcT46FVql1qM1RNe7LvmrmBKZwNuaSBzPo3EeVmXuYTqDQ/yN3fz+dNfcR8f4A3mAPwEN01fgWdQEuDCK4fVjxyfnqWwDrDVghBgZgButpKwN4uj2tLTn11uKMRa0A0Sy3PdyeTaei9IjoWYH/2pvpIJj2gWP8ckHbLk8eCDvQJBALr4ulKXra7qGtqi8CiNeM70H3i44hEbrjaXk6pOHFUhANz5eV7oEiX8BpPK4l7uM4TiGVa4TqyTa45Rb5W4U70CQQDlmlqYSJMSyOBMcM/xwCOnq4AgUOWh1SxqxtWXtQlXw3SA9adAB9ik7HjZLLQXB1p0izgRi99rDONli2RqoMifAkABPD126DukiTVuNl9h1TV0IJbIpGgR9t3azHuUR3nWciZgT2Gm59+e0qB0f4WpXOeIPDowoX0blMnEIfObyKD9AkBRy0oo4/nZAEy/jpTVx6AsFDGh0Y/stheLtmfTEsBQTqYLZvf9HI52OnPW0lEZvxnfWNVRkuW1qjK8MwtD3SF7AkB92/QCQaOgFzjweKzhaR9jQeUi5nc+9BN1Ai9ZwLaKjkznUfFDsZ+tDb5c5p0+GMvZImxEGmeYfqL6n1AmT69M</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAKEJBfhZ8TrSGL8LRkyG2Bh+qfm/8Oj4irfAAySYRme/fRGLfH+2K/tcGI0XywEJlSlmfhTkXu0l+0mgtcytU+hiV9PTA567DlWijltkssrEUCspT6SKWLviD0Bx47wIcASeVS8KUddcXhO3uXNijxX9MNo5DM6Cx+w34Uws5Hz7AgMBAAECgYAD8eolBuMLe1ki2P5cYpNJqlS0qxiWRHx1eu04yMg0w3KnauDeahKSwlNRpYsSF++BB6NAFMYkjiElURwTCw36ofcOI8W0TGtzDmLGKYkWfzOogCm+brzgXRagcBe4gvtP+u3+jm7FW9HOHf80T96XZZTlkiJRfXurC7u/Gql8XQJBAM5w7H8VRR+4DqZXPvbtU4ym7bcS06hH4Ef4khmvThCuRi/fRKFdBRJTZXac8w2jrSWckHmChILmYNwGt2SMLT0CQQDHsaFGuK7kzgeMtKv3QjtMC9QoIheuwLeSRuk6H3Hr/ETPkiQQP7eldhTkqF7+l37RofoEcOqZaG+hP56u5eaXAkBS9hyEYabavVvdyxf5oZw+3OKQ/NbkPKZMJf+IpOOJXo/EM0RgWIJuP+d5iE9AvvMZN1b0Ddh0xmJMacKPfKm9AkEAigvQmqwnM0L+UxW+34IorcxrkIbo6kSNYpCkwCpmvaU6CGhVh+oUUUzM6rk+Wi9uWwrnZFSOyRg6OzVYxD1n5wJAP584G7WFkjr/+idB0dpoYe6ubZi0gbIHxvz5SBYMd6sO1y5COQe2pY0wkgPShOrV8XEBi6wraKAdreuq5TOiVw==</t>
+  </si>
+  <si>
+    <t>MIICdwIBADANBgkqhkiG9w0BAQEFAASCAmEwggJdAgEAAoGBANONcr7d7AVeeTcxBw7G2CEIJ8hKM7T3p1BCNiyBoBstRNOToFXPx1zTawOVaqhXXlNyZkgBmoXwTC5r3uPF851131wYUmRaqKbuWgaqXJeB/ivZoiW5Eu1Ny4RU3g91iNAyWnL5xzwjH5gTr5g+51weBstxckJozK1ErtHkfWDzAgMBAAECgYAslvxQEaudSBfpk6pmqW/FqpfkBgvXAXohFwufHuVVxRlkNRIO9EATpzY/p583A09M7Gh1lezxfUA5aqAsxzz9GaBg2JmymfQIdYSwlGo6FM+QAjQPMYjnDS7fHk+p/ie04hVrwR/2dAxnzqTwxoZ9nj4vFWAETCo3ATlbeUK77QJBAPeKial4VRIwtRxsL2Davw5gtripkQX42Jg7T8kv0VoGIAc6p30dsLWHwbI3SCbkRi9JaPsEYdq2RpVRt9VqxM8CQQDayBYDNFQG5dEUzRnwC3DajTxP7A4DIhN8B8DhXGDlgLkWJiBy5D7Ej1fInihs56n+kf5nbzoSx9j6BljYWfKdAkBFsRBO0R0KUQI8bUztdMiDcMEgvkShLM02FsTAvKCxOrY7sszC0eAVS5JB7YR3xp7n40AWI8a0/8phca9S+4tLAkEArZWfUX+NQ8PH9jcdY0XQjrcMqWTjYT0CNKB6OtRu1Oki8R3jFQVff9kzjytda7sLN75iGXM4onoJ/6ZVi6MiSQJBALy//8KO3gmaozfG/SuOmoIAPzjTjs4JuB0GA+6m1VbqhH7v5NTf3idJCoZ/9/DSBd4uxMDIeO+86jubhtEWtjI=</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAKvLNWlQ0zZElAJi1c8M4OHapWAUbYPHkkzxoz5XNiCZ3A9NJ0/FunZRz7SmK3QRPwKIl56y32IGOYdhi3VWTw+vWvj+LVXHW+bQMZFMj/YGWAVoU2VelJl2PeBK+k8k3ZoThEbAR5mkdYUPexCUN60iwCpK91JtysuT7zEQQIjdAgMBAAECgYAmkk0PNNT/Ub1znbJItykEvL01ydBe7p+kA/r1g8pE3pbAnr+NUyVO7IZ4lniaKkcd8AIu4RVzolcnVNjlgvfj/B4uuQBc1nXWZvteq9jYuyIrGLdl2g5oEcyqifdUrf/b/c5qPvQamqQy+Z56q8ZGSeOnYLUHXa38EdUWAyAmJwJBAPA2lU23go59jbP9BqPmeKBK4xK4Gegd3yeZTcAgMG0iBb2jGmWZwlcmyZHwNX2CCjD4hKWZ4mzNh4D2AlwJkqsCQQC3FYReLQSgVIre/IAqCCZiRN9oNHj56Iz7ei1CPptv07FlRzyQA8AZBZlDbQN28A6mwvQls5cVm7q/au6W4RKXAkBhOdaIlEQ1pD/coAc2A6zDRExQYU+rEZwnDPfZUa4IHgMw1Hl0sh1k5QAlH5Km8CFr3MrjtDtfSnkUC368/ertAkB44nQr2n2bfzbSVNYq6oati9wW6c6W871iriEEBGKNS7FttcN/M3q7Cr9PjcMj3Q1PfpnF6vZvBgwgJ3KxnJqxAkAVrBA2FZG2555rnq3kDGF8rXEXKwz2CFQTXFHyM0zw9o8mMOrqS+qNr5zroG15owuAvlda7BZOjUSl5DtpBJ+g</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAMEIomkyXm47kosj21dvu+lT2IBlK4oCTpnF/nUVEj8j0m6vZaYfjgkPBzKMBVW3Al8z7fe0p7Ytec48srvDuS2DjAnNiXu2/ywxNE66oXtHaMELM8DRc5ZWSdJiav+BmsI3KsYp/ZqUgl4ZJ+6jUirXERsPYjo18WTFGM/vdGMnAgMBAAECgYBciN+WTzt+W1dqFPPKS/lIJlX0YstG2slEJOpQxRucofb38WPoiVrk08vu+rl5+AOOkM3EP1lgVxd7epRxtycWqVqVjH49hbYljOLZV78FygCrEXdq66LDKCWKJHLejZ72GTKZT/77xuNW5o0eRswKblQF/BjfSkXi8jjxipNNLQJBAOyzRUEoRRcTobwnt9iH3ZtCzZ+7kLycUBG20mCYSlRH5V2SfG+UV2897QX8QGhBPd4HPrUGhTvJzea4fE00mCMCQQDQxeV9BoPzeWr0XAH4m4hW2WX964ci6XrokSPJo3Q9tdqeu2JFW8IDDfhawHA/zEBqVjkAWq1UGv1lt44ds5ctAkAl8rvYrWceQwR8EPYVnfq2aKhkwoJ66qifnmruF5xbFMe+D70pemPmLsxwWDfPPx53GTxBc5Equ7jqE4vCKPt3AkAn0dcXpap9QedYfEQT+vZiOkztxYKc8hNzUFuXFgoRyyHLrMntmLbEhmGcTaAbSwXuQkvU+Xad2BgE0qHUoHBxAkEAmYIKzZ7j1YtQUTfU/r92CM+czFxI76Vdpe+vrr5xLNtyIUX0548Ue1OowtVzGdLNmp7rlis+9Gzg70CZFS+uYw==</t>
+  </si>
+  <si>
+    <t>MIICdwIBADANBgkqhkiG9w0BAQEFAASCAmEwggJdAgEAAoGBAJmMuHlzlZ5h5VspO8h6tIbgsoGrDrvG1EyeGj33N/lw6wFzrC9hz3KoRBtNn9iUXE8b2/A9+V3jsKqnBBJKz80GKKht2HKFDqMcA4Q6sSwSV2Dygr4GFMSjbdewNXTTjhgU4mq4GLhZgJjb0zagoE+XVaGLnL2SJj8O4WkKztDbAgMBAAECgYBJ/YE3JPdH5qx6jRf9twMeq0/ZI/Bpk5nhgZ3rliEm1b6oaHDkNCGegm6vKWyJFJSWmjoVPgfXskwDL4/KsLoItjgtWykcP01vyQUna6EAv4F29vTr6SZ7rvUUsJowq7tJbon7qJ4y79x2vt/EPcPqKT2a0THy1+JkWVedtjcSIQJBALtJ3fEWx1u2P04hmboSXPDFejravAt6OGCx3r5vC+uJ0HtxfLQFb6uv6933fc4pLhsswMJxsj0EA+chM1NZVaUCQQDR4hoQqXvhtBjIr9Ce1mp6XZx1mzV0NnF/dhDUFRBeb2/TIYi6z5U4FSt9PPDn7gk4pslBK0VcB8UYiyMGT8R/AkEAqMyDjzYDigIw/j9EaTMBtzOU3ZSlJQcL5wKJCkPVj31PfOKlDS9VHX1Z7V2Rco0k8/Ma7GVCysFirx76PmXmzQJBANDs9/FaJT1aH8m2aj+TRU8l3Fed9yoGABlXmAzmIvM+jtxm50q+1NWNDUuP3Gejpn5EWNaMknC4M1TpPCZORVUCQCzCkesyZa4mRTmgQWHw6VfLEnVJSm1g9QpuwM02310KG+2QjafoNXliMf3ZhMp4bfW+kkHqnzT1BR6O42j8O30=</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAKL4BpszGKRbItXYh70LecmBrq6HxqjlFCd3VPW/WEYIP77pKEKhTeJfN/j2W7WKUeuyFDhRzWJph8bzmkKwW8X6USCLcgWGcguVCwvX1o9HPsIzv3gW82QLultda1QYT6lnr9UM2B5UmMVIjiEd3ZKGvop7C2/nw+rTxPmzxVplAgMBAAECgYAff1VziJgiJ/UfJKbzfDTRI+3ZkKduPDw9dnxmtNFAU9bSNKkR27A8aM/eH+tQtoenyLbMvc62zxOteaaebgyGcptXdCv6rClhfW64e+j2lRv3zRXHYFAvB76ObA8uPQbz80scxfDKpSiX6kv2iFtC53dbodJqtFeAWWfkkD1yoQJBAK1nfnC7WMVCphhzyL4LPfDZNX9qOqHjnib1Ul9CnzCUJ54XyHPauoPako/aaiOqQFEGFDNINq4BEFdrWCikFFUCQQDwmA+tSJmSXaK6qf/L0nEyxi3iaXY1ErJXVTICHkWZpOlp0FCQwKozU43sxw9XsyOWzDx+eONA+OSsge6Vlr3RAkEAlC2jU6wUoIRisPSILzYmGSFT4Oyi6+I5LGtol3Sz2exQqn0CU1YvGit2IK1xE8cRrOs36dakuy63iyx0qk4D/QJAUbRSHpa5EGucB6gTpjQhHQ0QKAOIkR14UxArm2yMVlEas0R7F61WH3gQiohPPYkoXN2e7ZRAGKBth+fYDhTTAQJAHg9X+v6YRm1fPzEHYjItgQO7W6+PckAoPTgIuzGnl7ahH3UfFv+j4mFEHf1nLGyui1isf489vvcD1J6miB3CWA==</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAIIsEHgUgqKbPSE9fE2k4f6wZM5lUYLewdqu77KRNYGW0hHlumZC+2S9ByQN+JZDOLwS0NebEm7Ifx7oIFybWZX48VZs8ztVxFimlnpTAXrh5F1on01q4oo+P2/2Y19+6wPIwhyS31jf35P5kZpfC5AY3WjeiwD0tOFdo1Ifi3PPAgMBAAECgYASEJlsgLQsaszN+yFwCQzP8pzaw9bPCajvd02Og3ZgeJTIpQ/8Nxl6Pn1qNIImIEgUWawf78ZcF3kEygQLtgd1gmUNI4PHkdz5bKHwHLR9RNJy5jt1PS33EyhbQrGP+WCHZT9r5oFJ2Mso+NvAgPpMHypqU26p+nZZqQYsRvWHoQJBAISvPliwao7iGCmTuS7teAfDXTy2iDi++Y7P5HlN9CO3gOuG3n4TRrrW/GWZYsCbzc7p2DlNuS5Tm6RirUW4y1ECQQD7Jw6/Fuc/ntvt0KjNtIk/L4+I7Rd7EBuzluIRgnF+e9syYdtCDYDm8LrRZRS5S3IyWU3FjYRQ99ttxByV/kUfAkAYqERq0OYMhYG+AEDSsriyoKCsDrPD7+GKo6Gu1UjAdnKT0m14enaTdC5VZyrN5mZZxGU1SPdX35u18cyHf27xAkA1p611033J0LVphAdcEvKzRgTjGsvGZbWVU2mulfCLNgipJdDCtsHQFKPEslSQFXcrHHsJ9mbLKXh+ZcQ5ox2/AkBhVanYpfXTg4TZmKzEtUarWGokSQNk1PriKvQNmQsEYx8hQB2ol+buCIYNxSTXevuyzyJTzfs+gqHrHQEsxFbB</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAJbtugiCsqM+qX1dsubmf3DmmN93SfM9ZcYYAsyR/J2vIkO9yQDKOpH3rKspDp9B8SrD9BpG+t72BSoRhIOF9UXuawUGCWPBmkcrLUUT2zSdgvv8V7HG4DKMVDxXZfBuJzlmrCdf0Naqfl+m0OkGbDupWxn+qsBZjg8hFzSQ0cWZAgMBAAECgYAHHNfuC77Aa7UQF+jU8driprNgoJ4HDQctUTdcjaqygazjNV/yHhWpiFsGS+6I+dIUOlzYGi07caunomC01AzNdqRc5yoWTtR2YJQBw2Yy9eWntLGlwRnPrbodzt82B6mRCHzVlvx5Dk5em2FoX2CPRgQznP6DKUC+NjqblSMOCQJBAKkEuFhTiYaidIbe8ahMZZvuBH9JwPAMqnQsnJaDbpGgRsnszrQLa2T+2N9OKJskHPWcFniYZK6wgFl8UbWdiSUCQQDkmcTybOnHW6+Tp7FB3kS9pT7ovQE6/b1uAJ9MbOWrUzWU17WFQ7IThdVLjOJryN/IotIwZXtkQLHimZ30uOJlAkAWRaT1Hqz0rNumGiLGBqstDQRSsalW+JRNksNfohoj3nb1jNsAJrEUMfDqHCaFqxCV3OepJIu/6UpAgH1T7VpxAkAslq2ql4HV59VMWKYjceY4k3W80bjet8VuImLv9kGp9DX8TULTtouScUVUUiuL2IeFy/RxiinSOSg5Sbtck39dAkAmu5Amehe0BH7Ir09SX9YxtIRr4izLNcChlenAlFUzibVRxWH2YYP0S9N2Awfbs6lNbG+5sGWbgX97zrujL+/F</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBANbz+ZwMQDloFil0dIc4ufeHe8s/xQP26IxfWJy9knfHpvYe2R6nK03j1ImtQ541dMEpfsNn2hTwci7NbndiF/J3kBoSULm+zAbFBP9RAfhR9mElrjRCu/+U1fSxltZaS6eJR8eogCH6wAz609W+ENJGSp7b/lt4y9dO+BkINuo9AgMBAAECgYAY6dJ1O4GZcGQag5Sv9CtbB6PET7dPeXzELEGHz9GxOqgyICrXtStn4y9H58I4YjIOjfcobG8n0c3XeS2Y/lBlA6uBCCl4b1tfndQav0OhamjFzXSAhFhlAtVl5c6RTPB5b695Xo2exIeaopdQGCvStGdlovYB9ZyS7h25+5IQVwJBAPDVI/30U23hQ9EJF6LZ4miPHiRkTNA5zY3vPiCML53ki8vFfS4nKfJRgT4vPPk267E8CgEHSWRoXxrUGE548asCQQDkfZZkWqwE4QW49pDx+1P2cKErFLvBxOAa2cTmcJTbP5FstyP4v/QXHRkF8UOdMQa+av+dBqTZz+mC5gaf73u3AkEA5TLDrTXwjHs9Ulxn3TmlasMB+bpnDChmwzS0GL+xtX/Dt6t85gapug7thGPqkHc/Og6cqrvnkiJumJbPhyc9PwJAKxT292MVTjIzhwWOnOG7mhrweJQHNujtLILlGmId3x0kSXBaqvtehcEpx7IPAqOM1viLy8rF6H/IUrMWiq94DwJACzQ0XKtPXQAqSTF1RW+eRsTDLesfBnCbSW4/rvdrdo+thNV9lvSlmi3/IfUNY4XQA+ld4R7WBXuXhjlbt7RxFA==</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBALof+EXBY+wAAnqzvDRnDPziWDB0HqOhE12Pvd4GbKUT3Ee8I0qDixrPTVcJ2FQIXyASL+0mqDi8uQbEqWQylRMDOXZpm4ZrA4VPZk5naGAB7DC8jpQ3M9GqHRN1navTZ9J8Q/kBAB+JLB0zSTjiYjKJ1LR6iSxYeNdTwYT5oufDAgMBAAECgYADz6/HzeP76ywh0xhhglKzwvbHVzlhZGT/H3hl2X/UCYoTNfkLB5KLo/8TbzIs1lcMUxMEKix7rPGk/9XwJVEEH6b7wg9fVGrGBMT4h89H+z9dN68bMq7PuVBCyMujsoOVa5wBYhsvll7oYHeR1IsU+aO0NzOvE7qWh3qJHxK98QJBAPT0jSCZUhi/TaD3q60JAj/9cri7bl4X4Uy2Y6O3G8eD/h+foiUx8nrZHuiqjmLyEw3beNUlNtDQwD5R7SvWoz8CQQDChFspIHX7pEcHhOW6BuS2/ku9kDas2du9KmNQfAZJ1Vgj563S6/42q76yZ0nzoKr7pzva0ov1+tSvv5kF6E59AkBYggR8QunnBziFcPgXDapCdNF+7jpyxS4jCcP247Kl5Itt4cA0sFdtDAafCwFnvxAjcam3Wjr0OHk+C1wm+ucBAkA4PFGqozLY7JaIaviLfqCy8vPsuvvDnzxzBQUvaJvczqwrvTg4yXd2UNLR+yCbKbElDiU0zzgdhkXlBYx088N1AkEAp/F+ZzxobPDPUaIBgDW9ogRjcpFy0Q7vadEfXoGHYq7XgQp6eTg8jtKbfNBKYbHi+/TWbo7K+T++M60/wWMvWg==</t>
+  </si>
+  <si>
+    <t>MIICdwIBADANBgkqhkiG9w0BAQEFAASCAmEwggJdAgEAAoGBAKexOi9bAHgvvi07SgnJoqTIYrmtNc0B6Uzxr0DlUFxkA/auc/S1CyaaFrUVLfYV5Pk4/KUzAwHMau8eTwNwpciyqqM67G4A5iF9+o+MK0VlUnFRCIhwQT/YYsTqCJXVF9BecglRBRQBuB6FYxJLPZj+pmEeLcAciC8ZdS4whrZzAgMBAAECgYAgbZ/cX4NAOq9SrOf86461wgCBepLwYaG9nPEwoge/ziGMFyFaXZZZ8StZ+k4IjCRa45/LzIkU1HSLaDeMaUDNtZ+Th7oa84RyXdWb/wsFVzFjcJaDi04HSTMsS4mjBQd8p6BBvjHjFapLwW7M8fx1Irs/xi6WbWuk345T1MBk2QJBALY9e/SruwUadma2fsSDcWxUpSSun80R1rsFOXu40m2edjw3Hgv6bH1z6m94AKzfR0ILHGlUvaRXrd3kH7iPYfsCQQDrkGN5KcTblt5sLO4nl+cob4n6wxXl++EoD9tjCqOWH/w2l9mdvuPXgFwLxExQHfX3TIKJ9OIHWleoZe6+VkvpAkBvg+ohCyDy+4FuUsf5qlEysA0qCC1DCGJ0qLrHKY6ig2/oYvXg8ImIrvDK6wzGvA5XrILjNXaiZQDAogKDJkIXAkEAkyOVftFATYlnVVqbR8/ya6eAIEpLG2TBtyxwdOToWZWRDOi83XOnDaz30cHDiSetw9Lelx2HMeCUcHN7NRjiQQJBAKia+Ist5AwoG1HwZSzgGNfAcJBUXeytszpeyfhtDaxZh8fePP4DYQnwer/eDJb0hlvJ70cf9SQUAMg9BJ+Xts8=</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAJgUdV3webDVB/+3vC16BBh8rCMOsAOWLdlkxnRPdQRvqLttTwL0YYMM0DGyxh4775uqeC6tSR01ouf3Nvm6KTIUDBVQorEE0J3vtK5r3n3T52qhNATW4X4/DyMNeWCzCRmRUgwHF5p7varjSGZNvWzgaxK7++on5BZukvjLH6kFAgMBAAECgYADY1jkolK5UXTeA4XWEIgU7WAek5+9vYO6rZYgD+4baD5ro7xVJHfwrFSOEUpjI/KX9sTT+C9vDs6yjGCL6m14MGEy0euTQhcP57IX8/D8dOS+ZcrKiujYiHRtQe/whzysOIjV3V5YZDpeyzGm/opLpBgOXAVJRUicMlQR9XZS2QJBAPbinPfbJZrXr7I776AUYH13ALFZ9UbVV20GtHt2jY6wbIVtFvAXSzRbwqN77Uzf6T3MI6otSu9XqdOjVJskhIkCQQCdsc/RoYbTgzplad5Fhwx7jIxQaVtwfSqC26hXXIqt9YNXZuP+bRGyU6zDidjMvVNibkBH3TYjZcZYLH5+QRmdAkBFj0nMp8krnHObUznLr5IUJ5BhZ8gswfVU+ZumYZu2xUx+N2NMGDQPN39akpMkor3TtI2j6AkB8IAf6hfvclWJAkBosOSsYpU1FNkO/OMQu6DA4UVCGUAYhTBU4el33js/VFBXFTrl7ZkjD8QRqRFik4qpPVK1oxnPFEFCxn9P6H5NAkB/BTDxTTTpEeewDFU2x3MFsSt7Iu1tpCGEikbM06dY8HNQVOhteqsI6xaVdKjbx9G84WJHcfV19XGoodphQ3y2</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAM0SKlXOO+gmYZSWFU+1KF8dr5OUtwd/gg5X5Ih+6MPpFyMPumidRmIcvBTTQV4wYjAkOICRQHY9bnjvbm026jCUbMqGS+eyciDDDwvZsYZhUR+CgmMmmy7AFCCgAqXJhdcutynpHNDdK1eerd4nZisIZpHK5pgO8p/NfCbJ0T23AgMBAAECfzyczJE6uSTk3fK3vuoloXPQ/RRMiyIBjhoEizJ3papCOunMvEwvhZ4k4B1HqQqDQoJNh7sjM5UUkz0rh81qwyJly5uP60WmtapjNUghFaZnSgxw45GRb+WzrwEu5DSFBNasDGJesckslQBQLpbSHe5wmPS/1YsD4YNGY+oU4YECQQD/5Y+pzMI1WEmZoQb02e0RHav00qkzeJD5OiJ6NvEUEjiO/RXRBaJP5chj1ybvehQ8P+9tB9KvmAZhDCf7uv33AkEAzSdaW0dRzBsGMuEKhN8cvKu4IaIpLcJPfdZ5hgGm6bKwlfWoq49TFZzuUMYhN8n3l5zWMpj9JGd5UbMFGlbOQQJBAI0V3zhqGSVaMPIP8wrqYCdQqa8IupsTPTL712h0hERhq2dCqFWe+pd8hBhv1hqwvxlc0r/VUVbYxaOaFS1YMo8CQQCZnmgohYUYovvHSYAI8tCf7q3YcYcIPsIrZlhlIgOMZ0OXZvZAUPhT7Mj/Lv1cux1tKAG0rZ6QjfLoXHbrvCiBAkEAn27wbAOph2dHm6EKjaeB80q/s0yvrpJBfh892Xx28g206Z0ASke2QTISqD+7r0OYD4co0ZSt30q40jOHZ3vcYA==</t>
+  </si>
+  <si>
+    <t>MIICeAIBADANBgkqhkiG9w0BAQEFAASCAmIwggJeAgEAAoGBAK4m+bpOqhDXBAkBrKQbLGGDqRVW95ElKYLhPpnQn1FQWwcUAwwhgU+76rEpq7t2oeoUG4VC3M1sdyMzf/znVYj7keaGqOT1bGOYOecfV2fydVhkA0C2/EAoqxMS8b0NolkiH5P50HNA5CYPkMB1gIT0K2bjdG1s/xHXKrPt91YJAgMBAAECgYBNZ/qA0l0p7gAXprxfFsrjrvsVBpo0U/G/ADHseTuPD2neXAk8t5m74Hkg9LYltUWjfvt6gG0XC3pq1YWyWfp8lC0+Lo9zI0XbaDeX8QSQS07zr4UGbWHcmNmNM10BySHJRuUm5EPgxxNHIeGKWax225KMoo+wwqAwSCdqEWJ5BwJBANNZtxZp4rKjjB/OkvEOtSyelmkm7vZrXGEG/lktK7iVBU/EnVfQMCJdTy+/fVZZYfmRheLBcIRY0dvW73AKGmsCQQDS8YB9nK6ZKkok+DRds5Dztj2tE9p0p3VaO8stQO0C0IRtrTzClxibJjkPhf8uePtwmTxMqIknnkr7U1OAgFZbAkEAs0DEKB5mR1yu28s4lXsD7nQS3dxHkHg+QYzM7JWDH2pEtwLq8C+Co6LAJp8ijroAfssN4uRtqdIrK2mAamYnQQJBAJRQZxZqlrxsZotN1IvZWF5y0TSjE+MXZsSV7Aoab0qeT65JssHiuNNFcbM/dKc5Oxj1NNd1XFH10ySYdsqP8acCQQCfXaQht5lE2KD8YZTayj8pSHUzzHoEXMYQUOWWUPLiH25lu4q1rzafdcK1ofgK/XgOAY01twN8nC8njlpVIYs6</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAJKPIigzkzoOfLxQ69psxqfzAXj3OJzsJbKW4juSj2qi/+BxO03nUKSHeninXyLkz6Nkz+rty9VLvvIN2RZSJRwdRWFEGqd+jZIxamQXi39uQ1djmhXln3wBfZP/EhdgN+CePPHZAQNpbCgO5vS6baoiltXSYwceZXfPCrMn5BX7AgMBAAECgYADcGXuovN+ZPTw+MZe0IYCsQzJpFco+ffDkQ9wbc9fuTckMqtkqTSW7LH/8FTh8QodDoEop6Wu+cipRC2dJCoqufBT6VLHu68W3MX3o0s//0wqaIRI47iTTNOX6iBuGARaV5uqy1SnEuklJ2Tew+A1JTw1vCRbYCF9KmxdG8d7wQJBAMMvt38fUVFu8QyZzeBBjMoKGBRl1zMAHhc9jZOg0++hm1yTc950ueFC1Vr6oY86aWLg76/RS3qtylmhA5+CQ0cCQQDAONnYxAwphn2RhSxJc899bC8PtA/hmpzWJqZm+uhLm7eJMJ8hq4qNWXWl2+71sTARIWCYilXIgOlz05XL1+mtAkB7MV7LqWSV1UPnBBxg8n599qkEFtMgqW5UlNEK4HNjx8hbQeXb/ihj+N7YsV/PGrrxYa9mdN8C6zXQJEQ5JOp5AkAU/2DUq/3EH3viBJEk6PC2e7XcWkgN1ezh+9DbmPb9I2J2KwiHDg0Rib8vQgolbpiYlnPN1fau814NGATaApj1AkB24Ce9SIXzanGcP38JUMSg2OOEflvYkMX4ecLU4OcF8eozzAbQujeLiffe2o09zGDsK8E0B33ZlXUnRh6crH9j</t>
+  </si>
+  <si>
+    <t>MIICdwIBADANBgkqhkiG9w0BAQEFAASCAmEwggJdAgEAAoGBAIPty7a8/z8308QiaG6TFX0R9d0rQUCER17JOhapVc9Oe23cFUEJq3ereksHSZuMS/YBeKCvtnds/h2KBSnX8E/ssZjLE4kC5uj1SteRKNbAStnIyCJAJCq75kNpYVpPp3etAH0XIVwDxxARCN5nlX8PPDnezcQRssRzUBX/1i/tAgMBAAECgYAXhPepwsTQXOAEWcv7Vn5gtyh5PuJZoZtlowMXkiWpmQi5G6CwYQxv/6KEKK7vK5JJL5b1Mo4ZeVVOJ9Jm1MfS/kbwKteSdAovpH+P4bSz/CK68PIJTqWB0P7q4zvDYutFxR6VCbUGUbyTmiVFBTWeic82cMWrdFMZE7hOEKvFIQJBALzk1BzfXlAakx00w1h1zgsq2vz666OyaluR1mMpWGKX20VJjM/DFNEHIzXprxhoVjWKXInryKm/9ODl37sBZp0CQQCyzDjClkHHi4ovnf8/HhPD6Q0ZrLaibiA/tbQRdLiQLP1i/Cno84xBunNw3bXbEM/cAwpOAtrbZc2dZ+1OEgWRAkEAn4bR7KBoUlZfMCdDYw36uUu0LjrrjxA66qK74Hsmff2p3VZEaaJjjjTs87crfP2A8S6tAH30tge7k8QPsyt3sQJBAKn7ohLNCyiMrwlqKlp1W9ErZXr9SnzOOfaX5uOZlkXrn9JVbfq8YKG0gz/QaK4mI5dFhKx55lwjQwHc5i0M0SECQE3xR7pzQUAhLUCFCEYXDC2w7In3T4Solch8tnZ5Hq/1QKO3ywqL6TnLp26U94BKUJb3F3//XQ0bQ0v1J2T2SWo=</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAIgu4vftnTbXzkGrLKPAME1y/KqiVNd6Bl1UpQVKw3zjM/kGdpM+5IiKCzzxf8LshUxPljRqG582sUYTFPsWFr3t6iFS6kX29bmPz/NXO/QH2r6Db6WRmf5u8XtCMNasa+Pd6Fwghlrw4BCotY/VjiFulZCBtjLT8QbnsrFjOPlhAgMBAAECgYAJSYev0f2WjH5Qp8RolAyQ2GNEA8QQQEGID32D8Ea6qqGUI9oZGpq23d5iu2ZNVcuVZuWrqpzUBwSgVPoDHma4iikXJYmt/rjlrIIR+OjG4q3wXSxyOAU3MXXvXfdNnXA6DDlvD6MEIUQjpJIfRa9/k1nAnrhfUMlWfGfPy3aCLQJBAJ4wB6RD/ADOoqk3+ZSK+9RXUJzW0WPSbKNX5TtFiG4wIC6IMjpLWuJmMGqoIg3dqtQBG87+RiObojNWZ6zyZHMCQQDcY7T5SCN4aO/ZGiFjCg+FkaqNWGEu1N5oENCsnxqDOoWyCkaLwrTA8KpBxw3ceLpZkrRu74dDOgWItXKMFwnbAkEAh6Gm67Fe4VJLJcxYsoR4aBh1hgSqhGxnuaYjZi64S8H31e3xIwp5YqU73jdK+5iUYDKTJWffu6g16s6rFh6/AQJABUeWNEqYHvBUnpzTo+2/xXFh5pTxbw/GbDPK6/e7yN0ECunYGs0FS4H4ci70lA2IWVD8ZZPzZ5biPw4pulVq9QJAHAt+j1pNqlRuGizMgrDJcYykJtxnPTQj7/fomK/+B5f1aZhvA8l5t5Og2EP9ZtfDNhYevKVfrJHMfxmG0h7NWQ==</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAJC7LDGV70yIIDIv4diits4WUqzSbvZjVjXGrOQsIMP5sWwxmSqV0L5tmBv/+T0T2bK6KerUrSThcvS0j9dv7xEErgo6VRu1s6OVp9CAFP/XBTiDPEJNqs23MfmGrmKe7+zh9zE9+IXw6OzxyZukDqx7KXCHU2O2mFvjojzQdWj/AgMBAAECgYA8lAtoadByoRuQxhfq3BhV5GQQcDf/qw5/jbv5+TpxrMaFebEZcQGhYy/isF57IR7ivyciYohiQnciU51NWE2gl6TdnrN83DVM6q/u/UHZCSNJx358BhaeMC7KoA6jXgSZF2hAj0iuzExkZ/yfnYVHEjs11LG9bOIJmW6lWZe9SQJBAKOPbbK+QwvMlDMRou0qfxfU7/w6toepf+Qx1bRnH9cyG87yXQBeURP1Qmebg4hC9/I9bIcqBwKDO2c9gSznVFsCQQDih3gSU0YUsWWi4TIbks14MXXBNd5XlhInbpLCIXNvDhNCqHmSANg6kuGp0SVn8zHiY9qQsFPlpwlAv0UHos8tAkBj/hGwjwTqN736orOajrp4VWQKLdLdiVB4r8bYrZsXsrixghY9XWvv6acZNEfrjBWNcOPill0Gujgc28sXKq21AkEAoMza/d8g2yWF6RYEFLCjq9MoLIuJlhDQOC90e9t07ntGTsX67hotY37KM1pkPCLU4UhSaOzR0S4+EjjzzlTSzQJAeglO7tqo1VxEA1VLgKSl6UbEujRokgVv5Rk5EOYDSnhLgyHUBm20p5ne9Qjxq5Gf/2p5MzxoCj4C9Gf6HL9T8A==</t>
+  </si>
+  <si>
+    <t>MIICdQIBADANBgkqhkiG9w0BAQEFAASCAl8wggJbAgEAAoGBAJsFKav1u1QEaiqqm/Rd87HJbXkbCreplfV8cuk30QSYnGwKWaoQFnGWGf0rGSxdaSH0ntAY64oumYK97yGgEDoetQvvitIDA4ydqcVWSKeLqnvFJ3IIjcSIIiZk34a8N1PF+xhyy5LtKeEUl1Biz0uFyVShbt+G8ZqLSzgKYCSvAgMBAAECgYAIPh6Inuc07b7Dzp2LQU5tyh/3InAP8viSL7aGd902Ng0llRyBm+hgzF8Zl8Fdzm7o8ZjBYbA7tGpqMFvQn5h6AT5t3lCliGQnGarAzqUzwOYJjekU+spS48w0ksViKbJ4FcXi1koDRMwgIHtMRhEB08T3nhHWxwtGNYfp7gvzGQJBAObHxHLeFTeUfR3DebMBd6UKzZMwLQAezIZlD5ZZBp1ooVwbJSSdqVvQkfm5h6JHeC/DaPRU2m9w/cA/0k07rscCQQCr9fRWU1BHOMOQ1iKhXCdhBdXp5SHS3P9M2Tw7JSS7iH0a4Y78Ggk+pL10ZwaLliMETVuj04rbNsq8tcNoiRLZAkBNsSz6erdr2apxTbB3yeOshUGF7q8Hnla+W+FufRQUA/hmmKDdfdJZHZM3HfWCdUsJ0WBQ+Qv8fm5+vT2gUJpbAkAlOZISGej38f7L3L8UZSmVJDlBb7uZtQODNEeImirQeeRzLD7SriQwLmNgzmipUO/1n3VmCoY1nC/ZGBPcDkhJAkAmP3ERBjAn83IIZx2KK0bLNVdclrwowtQBG6SmKtQxj0xzODf6L1XWCOcJG0aSMXUctq2tOTuDoZWyEbh0jKO6</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAId+J0A1L5fRLJhKSLFzCqtdBWywJJLBh6QEesbIhgEnYbRSkok/+vGme24FHo7VEM5iVVqLxfRmWRbiHU+Wm+QX6d+hqAdfsrZf78uG7pYCSeDpqy1NEQDHla81Aga8dIBaqUIgheIOjXsYroUspq5+Q+PAcpgH1LFeX0SpraypAgMBAAECgYASeCZWkMlvivJmwf19vt5N9KyoH6ykmp/oQjoQPcZSgvFFGNpjviZxaU269hSvyKh1UZ8r7BCsW4U6YtE3B6MxNWpvEqrRtOI5SBskVBxerOeayWmGIkfTzzLrTyx2KttjJ4THfR+2Y3kU++xSFx0ay4sIhA5EMFzoPx0rBxa4jwJBAN3BQkakgWLd2r6DtGsENzkSpom4fOzZuwB90YOztDWZ4pGuC74wb8EwZ8qzPOoS9fMO+H0GVVQexzUFOUFn5O8CQQCcaqc12Yuy3zK1DcyJ1b5yYSWDOqwGlJppuY7qAj6orleb2Ybh0cG0AsfwT2NFON569q0TsByDkMJB10ScrXfnAkEAn8XlraZLPuOf/pJARLbV3v4sFaBiCfjaPoFoml644cHNN69R8KdPbb8lmStJIVGl+Yj4yoPsqN5AI1hvJ0vm6wJAMYOpjuhgyqzRFnNZzkA1W2vZPiNylVqxTsqIrRcs0qTt4s4HXrDRyrQeqrnWyPDprK8tts/HFvbaJ5GHjLl0/QJAe3WBqe6nbEP7RUfrq3y9cW06wKbJrwrTpv1/aQYHMxeicpoPvA7oUvihXmp1OjmEXh+ny4VDGmvQMkl9QjKiwQ==</t>
+  </si>
+  <si>
+    <t>MIICdgIBADANBgkqhkiG9w0BAQEFAASCAmAwggJcAgEAAoGBAOChpnsZFDH0g8WWT/S73CcbG3BCvIHhRT97Fr2nJVZzoSfdJMD9hpj7OSfvRkZHylzYS3udyWGgRr0rpnpGVl/I1x80VelJVznvBhBtARKWGPd+yVJmaESgcQruMeDxjrfq4hC4rnHvlt1f+4Fq7XVjctXDrfau5Z7QcuwAPPhRAgMBAAECgYAEsawSb3Q6FQN56gmysghIMutQXbyltCjnyjEv9mGz3Ee2VwsxEzswUDOiD4B28IIcjZKKO0JdjWVdB5/7dyPP45CZVvEg+NxzeBZrmVnHqtcbfHBNQZFsD4JzX8vnSKrz20XPiqxQYzydJLIQDyd7PaeI5U6HMMF7pBu3U9NIrwJBAOUC1hU4nckMllcTURgTM30LzSUncGfEwyEl7dDqj6Ng3v23HsW9UGGlkfi8SiYPb42ae3RqSf0ns6Na0D5PxGMCQQD7Gq61yRln6V+7HJWwdC1OLniqPRdjLGheNGxrdOnTmkMPcCTL/nw0rvT76S5BfrVWNtYWK+9gBXBAv5v7wqy7AkEAjXvgGYI98R0GsMstWatbLxEgb6jbCDEGwK73KxAPJ8fMXIFK0K2yQHGTKlHhmXwF1j0vsm+MQIvLrsuHRkfvswJAXy6MDyg9UyApQ3ngW9SN39bJsm4Z0WPh4+OnPUxB3g3ZYZ62tASw/B9diaen+veWsSl0GU9qG1G0bTa0X8g5RQJAJVxb+gTXi3i9Ah3wRhso20qtgOIKKw2YGCz+DGh9oahDKLFBwHumrDzGDf6Q+M5xZxhxasgyV+RToau7x+kQBA==</t>
+  </si>
+  <si>
+    <t>message from user 3</t>
   </si>
 </sst>
 </file>
@@ -74,22 +199,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="FG1:FI4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="FI1" t="s">
-        <v>5</v>
+      <c r="C1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2">
-      <c r="FG2" t="s">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4">
-      <c r="FH4" t="s">
-        <v>4</v>
+      <c r="B4" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/GFGsheet.xlsx
+++ b/GFGsheet.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>0�?v???0 ?	*�H��@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>message from user 3</t>
+  </si>
+  <si>
+    <t>i dont like the TV</t>
   </si>
 </sst>
 </file>
@@ -199,22 +202,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="D1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="C1" t="s">
-        <v>42</v>
+      <c r="F1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>42</v>
+      <c r="D2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="s">
-        <v>42</v>
+      <c r="E4" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/GFGsheet.xlsx
+++ b/GFGsheet.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
   <si>
     <t>0�?v???0 ?	*�H��@@ -202,21 +202,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="D1:F4"/>
+  <dimension ref="G1:L4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="F1" t="s">
+      <c r="I1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2">
-      <c r="D2" t="s">
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4">
-      <c r="E4" t="s">
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s">
         <v>43</v>
       </c>
     </row>

--- a/GFGsheet.xlsx
+++ b/GFGsheet.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="2">
   <si>
     <t>a message form vimpeli</t>
+  </si>
+  <si>
+    <t>a message form zeriab@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -59,7 +62,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -72,6 +75,12 @@
       <c r="I1" t="s">
         <v>0</v>
       </c>
+      <c r="L1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -82,6 +91,12 @@
       </c>
       <c r="G2" t="s">
         <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -94,6 +109,12 @@
       <c r="H4" t="s">
         <v>0</v>
       </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/GFGsheet.xlsx
+++ b/GFGsheet.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="2">
   <si>
     <t>a message form vimpeli</t>
   </si>
@@ -62,7 +62,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -79,6 +79,12 @@
         <v>1</v>
       </c>
       <c r="O1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -98,6 +104,12 @@
       <c r="M2" t="s">
         <v>1</v>
       </c>
+      <c r="P2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
@@ -115,6 +127,12 @@
       <c r="N4" t="s">
         <v>1</v>
       </c>
+      <c r="Q4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
